--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.06913551150476</v>
+        <v>1.798734520619523</v>
       </c>
       <c r="D2" t="n">
-        <v>10.31545320475617</v>
+        <v>1.676261145772878</v>
       </c>
       <c r="E2" t="n">
-        <v>12.75708320401197</v>
+        <v>2.073026020651945</v>
       </c>
       <c r="F2" t="n">
-        <v>15.62563748711686</v>
+        <v>2.53916609165649</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.71399093917312</v>
+        <v>7.428523527615632</v>
       </c>
       <c r="D3" t="n">
-        <v>45.83933722469819</v>
+        <v>7.448892299013457</v>
       </c>
       <c r="E3" t="n">
-        <v>12.75708320401197</v>
+        <v>2.073026020651945</v>
       </c>
       <c r="F3" t="n">
-        <v>15.62563748711686</v>
+        <v>2.53916609165649</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.89230210716161</v>
+        <v>5.994999092413762</v>
       </c>
       <c r="D4" t="n">
-        <v>36.35651963745735</v>
+        <v>5.907934441086819</v>
       </c>
       <c r="E4" t="n">
-        <v>12.75708320401197</v>
+        <v>2.073026020651945</v>
       </c>
       <c r="F4" t="n">
-        <v>15.62563748711686</v>
+        <v>2.53916609165649</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.91740261037035</v>
+        <v>7.624077924185182</v>
       </c>
       <c r="D5" t="n">
-        <v>57.87811488120322</v>
+        <v>9.405193668195524</v>
       </c>
       <c r="E5" t="n">
-        <v>12.75708320401197</v>
+        <v>2.073026020651945</v>
       </c>
       <c r="F5" t="n">
-        <v>15.62563748711686</v>
+        <v>2.53916609165649</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.99927243143462</v>
+        <v>7.312381770108126</v>
       </c>
       <c r="D6" t="n">
-        <v>45.02397049062168</v>
+        <v>7.316395204726023</v>
       </c>
       <c r="E6" t="n">
-        <v>12.75708320401197</v>
+        <v>2.073026020651945</v>
       </c>
       <c r="F6" t="n">
-        <v>15.62563748711686</v>
+        <v>2.53916609165649</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.49430929365425</v>
+        <v>5.767825260218816</v>
       </c>
       <c r="D7" t="n">
-        <v>31.03630355604771</v>
+        <v>5.043399327857752</v>
       </c>
       <c r="E7" t="n">
-        <v>12.75708320401197</v>
+        <v>2.073026020651945</v>
       </c>
       <c r="F7" t="n">
-        <v>15.62563748711686</v>
+        <v>2.53916609165649</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>56.55526954293515</v>
+        <v>9.190231300726962</v>
       </c>
       <c r="D8" t="n">
-        <v>60.9825137936752</v>
+        <v>9.90965849147222</v>
       </c>
       <c r="E8" t="n">
-        <v>12.75708320401197</v>
+        <v>2.073026020651945</v>
       </c>
       <c r="F8" t="n">
-        <v>15.62563748711686</v>
+        <v>2.53916609165649</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.67851957593614</v>
+        <v>7.747759431089624</v>
       </c>
       <c r="D9" t="n">
-        <v>54.88302642727781</v>
+        <v>8.918491794432644</v>
       </c>
       <c r="E9" t="n">
-        <v>12.75708320401197</v>
+        <v>2.073026020651945</v>
       </c>
       <c r="F9" t="n">
-        <v>15.62563748711686</v>
+        <v>2.53916609165649</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
